--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
@@ -1,205 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,2173 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>5.3483345018787688E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.1109334815442696</v>
+        <v>0.05348334901278643</v>
       </c>
       <c r="D2">
-        <v>0.1275626526162906</v>
+        <v>0.1109335174348779</v>
       </c>
       <c r="E2">
-        <v>0.1296510764576137</v>
+        <v>0.1275626910586339</v>
       </c>
       <c r="F2">
-        <v>0.18519184161256261</v>
+        <v>0.1296510990048063</v>
       </c>
       <c r="G2">
-        <v>0.26052142829382441</v>
+        <v>0.1851919335733466</v>
       </c>
       <c r="H2">
-        <v>0.25858561323823143</v>
+        <v>0.2605214429858539</v>
       </c>
       <c r="I2">
-        <v>0.30188221122903908</v>
+        <v>0.2585856245488202</v>
       </c>
       <c r="J2">
-        <v>0.38971266769634971</v>
+        <v>0.3018822227540526</v>
       </c>
       <c r="K2">
-        <v>0.37694762901717971</v>
+        <v>0.3897126732756995</v>
       </c>
       <c r="L2">
-        <v>0.4116603654905947</v>
+        <v>0.3769476307238619</v>
       </c>
       <c r="M2">
-        <v>0.44557119940844492</v>
+        <v>0.4116603450922761</v>
       </c>
       <c r="N2">
-        <v>0.43036962077203478</v>
+        <v>0.4455712291365957</v>
       </c>
       <c r="O2">
-        <v>0.42127416198012718</v>
+        <v>0.4303696548618361</v>
       </c>
       <c r="P2">
-        <v>0.40439843433689071</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4212741833119963</v>
+      </c>
+      <c r="Q2">
+        <v>0.4043984507665532</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>5.5302125896169077E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.3488141587862813</v>
+        <v>0.05530212865635409</v>
       </c>
       <c r="D3">
-        <v>0.43159157081511978</v>
+        <v>0.348814351132394</v>
       </c>
       <c r="E3">
-        <v>0.32808635100040362</v>
+        <v>0.4315915468162526</v>
       </c>
       <c r="F3">
-        <v>0.32969522063897022</v>
+        <v>0.3280863481122972</v>
       </c>
       <c r="G3">
-        <v>0.34667292276778572</v>
+        <v>0.3296952421852074</v>
       </c>
       <c r="H3">
-        <v>0.38020491519432709</v>
+        <v>0.346672845422896</v>
       </c>
       <c r="I3">
-        <v>0.41366323030280461</v>
+        <v>0.3802049828223138</v>
       </c>
       <c r="J3">
-        <v>0.42063371622703938</v>
+        <v>0.4136632411221542</v>
       </c>
       <c r="K3">
-        <v>0.41825700786014153</v>
+        <v>0.4206337075654646</v>
       </c>
       <c r="L3">
-        <v>0.44943925740747021</v>
+        <v>0.4182569858754775</v>
       </c>
       <c r="M3">
-        <v>0.48656629548309172</v>
+        <v>0.4494392217914367</v>
       </c>
       <c r="N3">
-        <v>0.54373651912790388</v>
+        <v>0.4865662304702433</v>
       </c>
       <c r="O3">
-        <v>0.59595744633086722</v>
+        <v>0.5437363272034748</v>
       </c>
       <c r="P3">
-        <v>0.59721132819741851</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.5959571746290886</v>
+      </c>
+      <c r="Q3">
+        <v>0.5972109630790243</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>4.7646709791184648E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>7.5920221033311336E-2</v>
+        <v>0.04764671147821904</v>
       </c>
       <c r="D4">
-        <v>0.171384315270497</v>
+        <v>0.07592033981248493</v>
       </c>
       <c r="E4">
-        <v>0.18896773530942851</v>
+        <v>0.1713842873158625</v>
       </c>
       <c r="F4">
-        <v>0.35627912504691728</v>
+        <v>0.18896774633042</v>
       </c>
       <c r="G4">
-        <v>0.32286720485019249</v>
+        <v>0.3562790835355844</v>
       </c>
       <c r="H4">
-        <v>0.29939590814054728</v>
+        <v>0.3228671258450765</v>
       </c>
       <c r="I4">
-        <v>0.36537451652651298</v>
+        <v>0.2993955667867381</v>
       </c>
       <c r="J4">
-        <v>0.40854357992663398</v>
+        <v>0.3653745778059266</v>
       </c>
       <c r="K4">
-        <v>0.43611262086831609</v>
+        <v>0.4085435160326099</v>
       </c>
       <c r="L4">
-        <v>0.44279253105856531</v>
+        <v>0.4361123866945423</v>
       </c>
       <c r="M4">
-        <v>0.44039804177343161</v>
+        <v>0.4427925814692247</v>
       </c>
       <c r="N4">
-        <v>0.44365202158862471</v>
+        <v>0.4403980360170955</v>
       </c>
       <c r="O4">
-        <v>0.45637717666488298</v>
+        <v>0.4436520252859758</v>
       </c>
       <c r="P4">
-        <v>0.49811364121054719</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4563771832618006</v>
+      </c>
+      <c r="Q4">
+        <v>0.4981136549910559</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.6309570625609718E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.16730704237347879</v>
+        <v>0.04630958086072079</v>
       </c>
       <c r="D5">
-        <v>0.21035163694963319</v>
+        <v>0.1673070839620528</v>
       </c>
       <c r="E5">
-        <v>0.45304789587920308</v>
+        <v>0.2103520024449833</v>
       </c>
       <c r="F5">
-        <v>0.31628510938599019</v>
+        <v>0.4530480464225619</v>
       </c>
       <c r="G5">
-        <v>0.38525536390628973</v>
+        <v>0.3162851493247131</v>
       </c>
       <c r="H5">
-        <v>0.38031282463972399</v>
+        <v>0.3852554029035725</v>
       </c>
       <c r="I5">
-        <v>0.37698903418431279</v>
+        <v>0.3803128322288001</v>
       </c>
       <c r="J5">
-        <v>0.34597106061792388</v>
+        <v>0.3769891024821947</v>
       </c>
       <c r="K5">
-        <v>0.34750133710701708</v>
+        <v>0.3459710585076358</v>
       </c>
       <c r="L5">
-        <v>0.3583163766079831</v>
+        <v>0.3475012496720429</v>
       </c>
       <c r="M5">
-        <v>0.37704324331716499</v>
+        <v>0.3583163696508528</v>
       </c>
       <c r="N5">
-        <v>0.4252044772058578</v>
+        <v>0.3770432159496778</v>
       </c>
       <c r="O5">
-        <v>0.46260796694169121</v>
+        <v>0.4252044208295492</v>
       </c>
       <c r="P5">
-        <v>0.50912391446051697</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4626078933165434</v>
+      </c>
+      <c r="Q5">
+        <v>0.5091238082714106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>3.9850279761545662E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.18366614109936871</v>
+        <v>0.0398502864603788</v>
       </c>
       <c r="D6">
-        <v>0.19508236352047131</v>
+        <v>0.1836662351805859</v>
       </c>
       <c r="E6">
-        <v>0.45130723937544881</v>
+        <v>0.1950825781267858</v>
       </c>
       <c r="F6">
-        <v>0.30016566897396513</v>
+        <v>0.4513072324594691</v>
       </c>
       <c r="G6">
-        <v>0.33154342473381188</v>
+        <v>0.3001657169695601</v>
       </c>
       <c r="H6">
-        <v>0.33987839236988421</v>
+        <v>0.3315434245870357</v>
       </c>
       <c r="I6">
-        <v>0.28916847917522942</v>
+        <v>0.3398783961731021</v>
       </c>
       <c r="J6">
-        <v>0.29456669091213972</v>
+        <v>0.289168462394115</v>
       </c>
       <c r="K6">
-        <v>0.30537809723068809</v>
+        <v>0.2945666183398836</v>
       </c>
       <c r="L6">
-        <v>0.32632404273344368</v>
+        <v>0.3053782059120187</v>
       </c>
       <c r="M6">
-        <v>0.34659729441113879</v>
+        <v>0.3263240523705841</v>
       </c>
       <c r="N6">
-        <v>0.37605952326493369</v>
+        <v>0.3465973005480671</v>
       </c>
       <c r="O6">
-        <v>0.38837597870062729</v>
+        <v>0.3760595313687219</v>
       </c>
       <c r="P6">
-        <v>0.43671193494030708</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3883759734970451</v>
+      </c>
+      <c r="Q6">
+        <v>0.4367119250939774</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>5.0372378653645911E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>8.3156509790031044E-2</v>
+        <v>0.05037238119799177</v>
       </c>
       <c r="D7">
-        <v>0.16885009569240161</v>
+        <v>0.08315651576905601</v>
       </c>
       <c r="E7">
-        <v>0.20914476738433449</v>
+        <v>0.168850060859141</v>
       </c>
       <c r="F7">
-        <v>0.33281379900149932</v>
+        <v>0.2091447967771191</v>
       </c>
       <c r="G7">
-        <v>0.38005379572348652</v>
+        <v>0.3328138179073938</v>
       </c>
       <c r="H7">
-        <v>0.34983876839534989</v>
+        <v>0.3800536048671529</v>
       </c>
       <c r="I7">
-        <v>0.30936124694395251</v>
+        <v>0.3498387569452454</v>
       </c>
       <c r="J7">
-        <v>0.38962522734039612</v>
+        <v>0.3093612220467782</v>
       </c>
       <c r="K7">
-        <v>0.42052712927109948</v>
+        <v>0.3896252153587672</v>
       </c>
       <c r="L7">
-        <v>0.44051994130482103</v>
+        <v>0.4205271998593283</v>
       </c>
       <c r="M7">
-        <v>0.45935917567577439</v>
+        <v>0.4405199796279902</v>
       </c>
       <c r="N7">
-        <v>0.42370965949408002</v>
+        <v>0.4593591645708802</v>
       </c>
       <c r="O7">
-        <v>0.43244862428016051</v>
+        <v>0.4237096585485293</v>
       </c>
       <c r="P7">
-        <v>0.45448271023067571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4324486379853162</v>
+      </c>
+      <c r="Q7">
+        <v>0.4544827235935519</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>4.5950672964934873E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>8.0160221473292742E-2</v>
+        <v>0.04595067199556405</v>
       </c>
       <c r="D8">
-        <v>0.17050009299828739</v>
+        <v>0.08016023282478539</v>
       </c>
       <c r="E8">
-        <v>0.32170118667197939</v>
+        <v>0.1705002027683127</v>
       </c>
       <c r="F8">
-        <v>0.32714445394571479</v>
+        <v>0.3217011483459006</v>
       </c>
       <c r="G8">
-        <v>0.29281384454727338</v>
+        <v>0.3271444541126338</v>
       </c>
       <c r="H8">
-        <v>0.33548198337673368</v>
+        <v>0.2928138224418567</v>
       </c>
       <c r="I8">
-        <v>0.35316639296204527</v>
+        <v>0.3354819949120278</v>
       </c>
       <c r="J8">
-        <v>0.36158671762014621</v>
+        <v>0.3531663781401702</v>
       </c>
       <c r="K8">
-        <v>0.37682348709146513</v>
+        <v>0.3615866759798383</v>
       </c>
       <c r="L8">
-        <v>0.40641576739809671</v>
+        <v>0.3768234600765543</v>
       </c>
       <c r="M8">
-        <v>0.40118914505849662</v>
+        <v>0.4064157472566886</v>
       </c>
       <c r="N8">
-        <v>0.40165868274306887</v>
+        <v>0.4011891412987617</v>
       </c>
       <c r="O8">
-        <v>0.41665500591088361</v>
+        <v>0.40165868660737</v>
       </c>
       <c r="P8">
-        <v>0.44875613451379331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4166550219337473</v>
+      </c>
+      <c r="Q8">
+        <v>0.4487561459460509</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>4.3598446448248007E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>7.5067672206909103E-2</v>
+        <v>0.04359844720845532</v>
       </c>
       <c r="D9">
-        <v>0.1724259506333877</v>
+        <v>0.075067723703289</v>
       </c>
       <c r="E9">
-        <v>0.30178660790726541</v>
+        <v>0.1724259563968877</v>
       </c>
       <c r="F9">
-        <v>0.29267016642401072</v>
+        <v>0.3017865378145487</v>
       </c>
       <c r="G9">
-        <v>0.25013111766638829</v>
+        <v>0.2926701658712741</v>
       </c>
       <c r="H9">
-        <v>0.28616463670316422</v>
+        <v>0.2501312797492752</v>
       </c>
       <c r="I9">
-        <v>0.28236317443110831</v>
+        <v>0.2861646031386718</v>
       </c>
       <c r="J9">
-        <v>0.28937062762100663</v>
+        <v>0.2823632118585518</v>
       </c>
       <c r="K9">
-        <v>0.29170859324146248</v>
+        <v>0.2893705816890805</v>
       </c>
       <c r="L9">
-        <v>0.33336029264523109</v>
+        <v>0.291708588584678</v>
       </c>
       <c r="M9">
-        <v>0.309613783764013</v>
+        <v>0.3333603086726091</v>
       </c>
       <c r="N9">
-        <v>0.3115794753527763</v>
+        <v>0.309613796672701</v>
       </c>
       <c r="O9">
-        <v>0.31960019740103318</v>
+        <v>0.3115795115205684</v>
       </c>
       <c r="P9">
-        <v>0.33976628124955538</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3196002405792672</v>
+      </c>
+      <c r="Q9">
+        <v>0.3397663191842347</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.1877415907953887E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>7.0595506763611524E-2</v>
+        <v>0.04187741821745627</v>
       </c>
       <c r="D10">
-        <v>0.15894140410374949</v>
+        <v>0.07059553063720231</v>
       </c>
       <c r="E10">
-        <v>0.278140953553774</v>
+        <v>0.1589415417218198</v>
       </c>
       <c r="F10">
-        <v>0.27621022214855889</v>
+        <v>0.2781408752515704</v>
       </c>
       <c r="G10">
-        <v>0.23691337791987921</v>
+        <v>0.2762102106709788</v>
       </c>
       <c r="H10">
-        <v>0.26344504467297247</v>
+        <v>0.2369133787899278</v>
       </c>
       <c r="I10">
-        <v>0.26839805831534502</v>
+        <v>0.2634450580825032</v>
       </c>
       <c r="J10">
-        <v>0.27515869559963141</v>
+        <v>0.2683980388934908</v>
       </c>
       <c r="K10">
-        <v>0.28190437710658772</v>
+        <v>0.2751586538986138</v>
       </c>
       <c r="L10">
-        <v>0.32050459944951137</v>
+        <v>0.2819043847598836</v>
       </c>
       <c r="M10">
-        <v>0.29038879491035879</v>
+        <v>0.3205046220518647</v>
       </c>
       <c r="N10">
-        <v>0.29398226991595011</v>
+        <v>0.2903888039032952</v>
       </c>
       <c r="O10">
-        <v>0.31136655366391869</v>
+        <v>0.2939823039284519</v>
       </c>
       <c r="P10">
-        <v>0.33470840656863288</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.311366598274732</v>
+      </c>
+      <c r="Q10">
+        <v>0.3347084384240207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>4.6738063074199282E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>7.6678040525676575E-2</v>
+        <v>0.04673806392640889</v>
       </c>
       <c r="D11">
-        <v>0.16771446279671451</v>
+        <v>0.07667807691977056</v>
       </c>
       <c r="E11">
-        <v>0.29700889794512642</v>
+        <v>0.1677146983561901</v>
       </c>
       <c r="F11">
-        <v>0.28981885812985508</v>
+        <v>0.2970088630500104</v>
       </c>
       <c r="G11">
-        <v>0.25779627006099298</v>
+        <v>0.2898188680165057</v>
       </c>
       <c r="H11">
-        <v>0.29229700772365541</v>
+        <v>0.2577962648691881</v>
       </c>
       <c r="I11">
-        <v>0.30024946168438199</v>
+        <v>0.2922975796982135</v>
       </c>
       <c r="J11">
-        <v>0.30555430255547661</v>
+        <v>0.3002378429847063</v>
       </c>
       <c r="K11">
-        <v>0.29542736393401758</v>
+        <v>0.3055526134064129</v>
       </c>
       <c r="L11">
-        <v>0.32532606672946229</v>
+        <v>0.2954273730398548</v>
       </c>
       <c r="M11">
-        <v>0.30487817911518272</v>
+        <v>0.325326082840437</v>
       </c>
       <c r="N11">
-        <v>0.30406577728503942</v>
+        <v>0.3048781923885974</v>
       </c>
       <c r="O11">
-        <v>0.32390403897306702</v>
+        <v>0.3040658069483879</v>
       </c>
       <c r="P11">
-        <v>0.33236476004080662</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3239040814877915</v>
+      </c>
+      <c r="Q11">
+        <v>0.3323648247442646</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.2543650516439158E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.1547330652668534</v>
+        <v>0.04254365467548001</v>
       </c>
       <c r="D12">
-        <v>0.20426911637204689</v>
+        <v>0.1547331016517692</v>
       </c>
       <c r="E12">
-        <v>0.39814031567535818</v>
+        <v>0.2042695320999124</v>
       </c>
       <c r="F12">
-        <v>0.36338141114878852</v>
+        <v>0.39814031909888</v>
       </c>
       <c r="G12">
-        <v>0.44357095315044442</v>
+        <v>0.3633814308846576</v>
       </c>
       <c r="H12">
-        <v>0.37743903330138101</v>
+        <v>0.4435709771488401</v>
       </c>
       <c r="I12">
-        <v>0.34930802840884612</v>
+        <v>0.3774390353966153</v>
       </c>
       <c r="J12">
-        <v>0.3250177759616652</v>
+        <v>0.349308090499442</v>
       </c>
       <c r="K12">
-        <v>0.32373156207134002</v>
+        <v>0.3250177714896683</v>
       </c>
       <c r="L12">
-        <v>0.33668262285562289</v>
+        <v>0.323731524886342</v>
       </c>
       <c r="M12">
-        <v>0.35095642164934171</v>
+        <v>0.3366825806696265</v>
       </c>
       <c r="N12">
-        <v>0.39277807210170251</v>
+        <v>0.3509563864492431</v>
       </c>
       <c r="O12">
-        <v>0.42272801174032892</v>
+        <v>0.3927780275870414</v>
       </c>
       <c r="P12">
-        <v>0.48601230573187171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4227279367609459</v>
+      </c>
+      <c r="Q12">
+        <v>0.4860121873264207</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>5.7761211552443362E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.28984712988970768</v>
+        <v>0.05776122701033388</v>
       </c>
       <c r="D13">
-        <v>0.29244237750647489</v>
+        <v>0.289847173437656</v>
       </c>
       <c r="E13">
-        <v>0.44031664980542251</v>
+        <v>0.2924424059237587</v>
       </c>
       <c r="F13">
-        <v>0.48722725336027062</v>
+        <v>0.4403167741630155</v>
       </c>
       <c r="G13">
-        <v>0.46386330428498479</v>
+        <v>0.4872272942120399</v>
       </c>
       <c r="H13">
-        <v>0.5444378937859683</v>
+        <v>0.4638633322169202</v>
       </c>
       <c r="I13">
-        <v>0.55065138217385701</v>
+        <v>0.5444379331654209</v>
       </c>
       <c r="J13">
-        <v>0.53449370393197015</v>
+        <v>0.550651335477472</v>
       </c>
       <c r="K13">
-        <v>0.50986941533696784</v>
+        <v>0.5344936956780124</v>
       </c>
       <c r="L13">
-        <v>0.5180871465599769</v>
+        <v>0.5098694143256175</v>
       </c>
       <c r="M13">
-        <v>0.52781042538132406</v>
+        <v>0.5180871406080535</v>
       </c>
       <c r="N13">
-        <v>0.53840379941134786</v>
+        <v>0.5278104056010782</v>
       </c>
       <c r="O13">
-        <v>0.53682564511574071</v>
+        <v>0.5384037507286684</v>
       </c>
       <c r="P13">
-        <v>0.56482827519540346</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5368255438291448</v>
+      </c>
+      <c r="Q13">
+        <v>0.5648281513861724</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.7128445789057088E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>7.7045065425402445E-2</v>
+        <v>0.04712844509418141</v>
       </c>
       <c r="D14">
-        <v>0.15913184820237611</v>
+        <v>0.07704508869932747</v>
       </c>
       <c r="E14">
-        <v>0.1995411591367888</v>
+        <v>0.1591318446358092</v>
       </c>
       <c r="F14">
-        <v>0.30952999189281849</v>
+        <v>0.1995412465368443</v>
       </c>
       <c r="G14">
-        <v>0.34398584231050328</v>
+        <v>0.3095300983867437</v>
       </c>
       <c r="H14">
-        <v>0.30937336008536992</v>
+        <v>0.3439857879366596</v>
       </c>
       <c r="I14">
-        <v>0.26571603303995539</v>
+        <v>0.3093733801942725</v>
       </c>
       <c r="J14">
-        <v>0.32154297030656331</v>
+        <v>0.2657160451109976</v>
       </c>
       <c r="K14">
-        <v>0.35817413196527692</v>
+        <v>0.3215429688457595</v>
       </c>
       <c r="L14">
-        <v>0.36106684639228009</v>
+        <v>0.3581740411384179</v>
       </c>
       <c r="M14">
-        <v>0.35576097841057253</v>
+        <v>0.361067008203001</v>
       </c>
       <c r="N14">
-        <v>0.33342329976867202</v>
+        <v>0.355760996536535</v>
       </c>
       <c r="O14">
-        <v>0.3405607169712655</v>
+        <v>0.3334233159790975</v>
       </c>
       <c r="P14">
-        <v>0.33981971886600681</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3405607355763106</v>
+      </c>
+      <c r="Q14">
+        <v>0.3398197492389048</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>4.381244659732568E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>7.2128339760264309E-2</v>
+        <v>0.04381244763105494</v>
       </c>
       <c r="D15">
-        <v>0.1478410592527484</v>
+        <v>0.072128362762621</v>
       </c>
       <c r="E15">
-        <v>0.1783372894058029</v>
+        <v>0.1478411261812312</v>
       </c>
       <c r="F15">
-        <v>0.27830318683197369</v>
+        <v>0.1783373032805699</v>
       </c>
       <c r="G15">
-        <v>0.31514376975502439</v>
+        <v>0.2783031821072122</v>
       </c>
       <c r="H15">
-        <v>0.27638716882987258</v>
+        <v>0.3151436161462037</v>
       </c>
       <c r="I15">
-        <v>0.25250926202669383</v>
+        <v>0.2763871226445845</v>
       </c>
       <c r="J15">
-        <v>0.30323242205048961</v>
+        <v>0.252509267124326</v>
       </c>
       <c r="K15">
-        <v>0.34842250963256433</v>
+        <v>0.3032324158171503</v>
       </c>
       <c r="L15">
-        <v>0.35934449275766023</v>
+        <v>0.3484225459071306</v>
       </c>
       <c r="M15">
-        <v>0.35348129499412317</v>
+        <v>0.3593445042597983</v>
       </c>
       <c r="N15">
-        <v>0.33155805393556692</v>
+        <v>0.3534813192157874</v>
       </c>
       <c r="O15">
-        <v>0.33930106199681798</v>
+        <v>0.3315580792087048</v>
       </c>
       <c r="P15">
-        <v>0.34299578606650533</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3393010956364442</v>
+      </c>
+      <c r="Q15">
+        <v>0.3429958265669896</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>5.0841634388884928E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>8.1749906124201951E-2</v>
+        <v>0.05084163422853956</v>
       </c>
       <c r="D16">
-        <v>0.15862121456403469</v>
+        <v>0.08174990268879634</v>
       </c>
       <c r="E16">
-        <v>0.19103240731513119</v>
+        <v>0.1586211934422879</v>
       </c>
       <c r="F16">
-        <v>0.29549242294921491</v>
+        <v>0.1910324136627783</v>
       </c>
       <c r="G16">
-        <v>0.32940429273386163</v>
+        <v>0.2954923910288983</v>
       </c>
       <c r="H16">
-        <v>0.28981839648012708</v>
+        <v>0.3294042148164388</v>
       </c>
       <c r="I16">
-        <v>0.24821799490493271</v>
+        <v>0.2898183883452571</v>
       </c>
       <c r="J16">
-        <v>0.30694326145122958</v>
+        <v>0.2482180213545463</v>
       </c>
       <c r="K16">
-        <v>0.34828654637431189</v>
+        <v>0.3069432364096286</v>
       </c>
       <c r="L16">
-        <v>0.36110500112010879</v>
+        <v>0.3482866340493839</v>
       </c>
       <c r="M16">
-        <v>0.35240069031375892</v>
+        <v>0.3611049423520284</v>
       </c>
       <c r="N16">
-        <v>0.32870167210206819</v>
+        <v>0.3524006835851212</v>
       </c>
       <c r="O16">
-        <v>0.33039174730935428</v>
+        <v>0.3287016946248713</v>
       </c>
       <c r="P16">
-        <v>0.33215084840556469</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3303917732826626</v>
+      </c>
+      <c r="Q16">
+        <v>0.3321508963469103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>4.604856529385528E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>6.8922906674370552E-2</v>
+        <v>0.04604856692132987</v>
       </c>
       <c r="D17">
-        <v>0.1464982027046684</v>
+        <v>0.0689229311314484</v>
       </c>
       <c r="E17">
-        <v>0.17780623504288781</v>
+        <v>0.1464981906532467</v>
       </c>
       <c r="F17">
-        <v>0.28805711094005287</v>
+        <v>0.17780621744111</v>
       </c>
       <c r="G17">
-        <v>0.32392789743008849</v>
+        <v>0.2880571523946388</v>
       </c>
       <c r="H17">
-        <v>0.29463112275101849</v>
+        <v>0.323928105940783</v>
       </c>
       <c r="I17">
-        <v>0.26048453228532997</v>
+        <v>0.2946311472354823</v>
       </c>
       <c r="J17">
-        <v>0.29892013573100762</v>
+        <v>0.2604845554682627</v>
       </c>
       <c r="K17">
-        <v>0.34976222083550718</v>
+        <v>0.2989201238157206</v>
       </c>
       <c r="L17">
-        <v>0.36026733724195159</v>
+        <v>0.3497621867089722</v>
       </c>
       <c r="M17">
-        <v>0.34957738236934499</v>
+        <v>0.3602659118910224</v>
       </c>
       <c r="N17">
-        <v>0.33495716488869509</v>
+        <v>0.3495759530038777</v>
       </c>
       <c r="O17">
-        <v>0.34426101683197352</v>
+        <v>0.3349572145380592</v>
       </c>
       <c r="P17">
-        <v>0.33545999969046603</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3442610358263931</v>
+      </c>
+      <c r="Q17">
+        <v>0.3354600361561691</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.4631846224815919E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.16626204059303809</v>
+        <v>0.04463185108986992</v>
       </c>
       <c r="D18">
-        <v>0.20882504556721479</v>
+        <v>0.1662620434469551</v>
       </c>
       <c r="E18">
-        <v>0.42187966669483368</v>
+        <v>0.2088254380264647</v>
       </c>
       <c r="F18">
-        <v>0.33611048100747509</v>
+        <v>0.4218796892394462</v>
       </c>
       <c r="G18">
-        <v>0.40560330122882082</v>
+        <v>0.3361105018359921</v>
       </c>
       <c r="H18">
-        <v>0.44955328114654403</v>
+        <v>0.4056033497413695</v>
       </c>
       <c r="I18">
-        <v>0.38466774048748598</v>
+        <v>0.4495532684494589</v>
       </c>
       <c r="J18">
-        <v>0.33071469870306958</v>
+        <v>0.3846676835354735</v>
       </c>
       <c r="K18">
-        <v>0.32517510689741952</v>
+        <v>0.3307143027359474</v>
       </c>
       <c r="L18">
-        <v>0.34712908412936222</v>
+        <v>0.3251750609667746</v>
       </c>
       <c r="M18">
-        <v>0.36295299314470408</v>
+        <v>0.3471290901116849</v>
       </c>
       <c r="N18">
-        <v>0.41657610462921218</v>
+        <v>0.3629529559683808</v>
       </c>
       <c r="O18">
-        <v>0.45892686202326499</v>
+        <v>0.4165760477995011</v>
       </c>
       <c r="P18">
-        <v>0.50207700239185771</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4589267603498082</v>
+      </c>
+      <c r="Q18">
+        <v>0.5020768679601246</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>5.2708975902415613E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.19710557021720779</v>
+        <v>0.05270899782638649</v>
       </c>
       <c r="D19">
-        <v>0.21232151785044509</v>
+        <v>0.1971056430308315</v>
       </c>
       <c r="E19">
-        <v>0.4476623946971352</v>
+        <v>0.2123218157650856</v>
       </c>
       <c r="F19">
-        <v>0.29778995709485362</v>
+        <v>0.4476624285322294</v>
       </c>
       <c r="G19">
-        <v>0.30966579726546878</v>
+        <v>0.2977899426687186</v>
       </c>
       <c r="H19">
-        <v>0.29052595681676557</v>
+        <v>0.3096658358551866</v>
       </c>
       <c r="I19">
-        <v>0.27290818776344788</v>
+        <v>0.2905259791094383</v>
       </c>
       <c r="J19">
-        <v>0.26582541878598182</v>
+        <v>0.2729081988821403</v>
       </c>
       <c r="K19">
-        <v>0.28484306209978838</v>
+        <v>0.2658254198709241</v>
       </c>
       <c r="L19">
-        <v>0.30517169705926189</v>
+        <v>0.2848430707644367</v>
       </c>
       <c r="M19">
-        <v>0.33473542947227591</v>
+        <v>0.3051717140580066</v>
       </c>
       <c r="N19">
-        <v>0.3773884746644558</v>
+        <v>0.3347354503887687</v>
       </c>
       <c r="O19">
-        <v>0.38344733055633923</v>
+        <v>0.3773884914702983</v>
       </c>
       <c r="P19">
-        <v>0.41661820893305762</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3834473426200031</v>
+      </c>
+      <c r="Q19">
+        <v>0.416618197446587</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.4485022521757893E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.23531330454122301</v>
+        <v>0.04448502237627566</v>
       </c>
       <c r="D20">
-        <v>0.22680532155186339</v>
+        <v>0.2353134935409747</v>
       </c>
       <c r="E20">
-        <v>0.25887628552903802</v>
+        <v>0.2268053748122241</v>
       </c>
       <c r="F20">
-        <v>0.24321915615810771</v>
+        <v>0.2588762039471974</v>
       </c>
       <c r="G20">
-        <v>0.31523910129096161</v>
+        <v>0.2432191545158909</v>
       </c>
       <c r="H20">
-        <v>0.26754444153885198</v>
+        <v>0.3152391673032643</v>
       </c>
       <c r="I20">
-        <v>0.26843646866376458</v>
+        <v>0.2675444516678366</v>
       </c>
       <c r="J20">
-        <v>0.25777983526003112</v>
+        <v>0.2684364577374624</v>
       </c>
       <c r="K20">
-        <v>0.27664016472779451</v>
+        <v>0.2577798341268897</v>
       </c>
       <c r="L20">
-        <v>0.30881278412936403</v>
+        <v>0.2766401719093616</v>
       </c>
       <c r="M20">
-        <v>0.34160731662558952</v>
+        <v>0.3088128158752609</v>
       </c>
       <c r="N20">
-        <v>0.32492157931961191</v>
+        <v>0.3416073505733166</v>
       </c>
       <c r="O20">
-        <v>0.34562641902032032</v>
+        <v>0.3249216038507932</v>
       </c>
       <c r="P20">
-        <v>0.36018100983053047</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3456264221508145</v>
+      </c>
+      <c r="Q20">
+        <v>0.3601810042533067</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>5.7176475485445313E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.34474415971313699</v>
+        <v>0.05717647778153574</v>
       </c>
       <c r="D21">
-        <v>0.40668686118984071</v>
+        <v>0.3447443433604509</v>
       </c>
       <c r="E21">
-        <v>0.3313433419076921</v>
+        <v>0.406686832113315</v>
       </c>
       <c r="F21">
-        <v>0.32543181557040451</v>
+        <v>0.3313433619958487</v>
       </c>
       <c r="G21">
-        <v>0.36575660344129007</v>
+        <v>0.3254315281908414</v>
       </c>
       <c r="H21">
-        <v>0.42374609914788969</v>
+        <v>0.3657565960999175</v>
       </c>
       <c r="I21">
-        <v>0.44360566102029819</v>
+        <v>0.4237462200108272</v>
       </c>
       <c r="J21">
-        <v>0.42507917619999541</v>
+        <v>0.4436056569674898</v>
       </c>
       <c r="K21">
-        <v>0.43507926831507038</v>
+        <v>0.4250791359987233</v>
       </c>
       <c r="L21">
-        <v>0.4537754329631804</v>
+        <v>0.4350792262628373</v>
       </c>
       <c r="M21">
-        <v>0.49557340052158971</v>
+        <v>0.4537753591523938</v>
       </c>
       <c r="N21">
-        <v>0.56537977459443656</v>
+        <v>0.4955732687893751</v>
       </c>
       <c r="O21">
-        <v>0.62750357631847886</v>
+        <v>0.5653795671637056</v>
       </c>
       <c r="P21">
-        <v>0.63491165835103869</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.6275032558986158</v>
+      </c>
+      <c r="Q21">
+        <v>0.6349112814769964</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>5.7797712280034608E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.3374797893897219</v>
+        <v>0.05779771486506086</v>
       </c>
       <c r="D22">
-        <v>0.39646441032717428</v>
+        <v>0.3374799839402095</v>
       </c>
       <c r="E22">
-        <v>0.31824179318065687</v>
+        <v>0.3964644104072913</v>
       </c>
       <c r="F22">
-        <v>0.3256039193335899</v>
+        <v>0.3182417610260926</v>
       </c>
       <c r="G22">
-        <v>0.36379129549259148</v>
+        <v>0.325603898466612</v>
       </c>
       <c r="H22">
-        <v>0.44394322547393472</v>
+        <v>0.3637913971565646</v>
       </c>
       <c r="I22">
-        <v>0.49173642863457162</v>
+        <v>0.4439432212555752</v>
       </c>
       <c r="J22">
-        <v>0.47595550657362629</v>
+        <v>0.4917363894846437</v>
       </c>
       <c r="K22">
-        <v>0.4834510796783828</v>
+        <v>0.4759554233212774</v>
       </c>
       <c r="L22">
-        <v>0.50807319067670553</v>
+        <v>0.4834509945869812</v>
       </c>
       <c r="M22">
-        <v>0.52960895991398527</v>
+        <v>0.50807309850661</v>
       </c>
       <c r="N22">
-        <v>0.5815422034683303</v>
+        <v>0.5296088039974687</v>
       </c>
       <c r="O22">
-        <v>0.60869769659375494</v>
+        <v>0.5815419416748495</v>
       </c>
       <c r="P22">
-        <v>0.63116209553977898</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.6086973416133847</v>
+      </c>
+      <c r="Q22">
+        <v>0.6311616517676448</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>4.5568968474300683E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.26821987763124788</v>
+        <v>0.04556899831362478</v>
       </c>
       <c r="D23">
-        <v>0.27798319431056617</v>
+        <v>0.2682197621272621</v>
       </c>
       <c r="E23">
-        <v>0.21938204127657729</v>
+        <v>0.2779832206803258</v>
       </c>
       <c r="F23">
-        <v>0.29933849313399291</v>
+        <v>0.2193819392315356</v>
       </c>
       <c r="G23">
-        <v>0.29664545030764572</v>
+        <v>0.2993383125482157</v>
       </c>
       <c r="H23">
-        <v>0.31621432057981907</v>
+        <v>0.2966454670050848</v>
       </c>
       <c r="I23">
-        <v>0.36350094291558771</v>
+        <v>0.3162143330251473</v>
       </c>
       <c r="J23">
-        <v>0.37906551879827549</v>
+        <v>0.3635009436418505</v>
       </c>
       <c r="K23">
-        <v>0.43223481903895378</v>
+        <v>0.3790654844654587</v>
       </c>
       <c r="L23">
-        <v>0.46154661378231171</v>
+        <v>0.432234665759946</v>
       </c>
       <c r="M23">
-        <v>0.51922050051765112</v>
+        <v>0.4615463867216211</v>
       </c>
       <c r="N23">
-        <v>0.54352307463788385</v>
+        <v>0.5192201263015355</v>
       </c>
       <c r="O23">
-        <v>0.55432636755310005</v>
+        <v>0.5435226423176339</v>
       </c>
       <c r="P23">
-        <v>0.59263478141691306</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.5543259133100997</v>
+      </c>
+      <c r="Q23">
+        <v>0.5926342972764433</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>7.4267070811828664E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.14160141564911349</v>
+        <v>0.07426708082048382</v>
       </c>
       <c r="D24">
-        <v>0.23733973398086039</v>
+        <v>0.1416013667046727</v>
       </c>
       <c r="E24">
-        <v>0.22675186891591681</v>
+        <v>0.237339758728859</v>
       </c>
       <c r="F24">
-        <v>0.24206948010612989</v>
+        <v>0.2267517230751314</v>
       </c>
       <c r="G24">
-        <v>0.2309171556696184</v>
+        <v>0.2420694454715739</v>
       </c>
       <c r="H24">
-        <v>0.31246212856997557</v>
+        <v>0.2309171079912935</v>
       </c>
       <c r="I24">
-        <v>0.45399965019281441</v>
+        <v>0.3124621302324028</v>
       </c>
       <c r="J24">
-        <v>0.46809719399851729</v>
+        <v>0.45399992130716</v>
       </c>
       <c r="K24">
-        <v>0.46622042154120991</v>
+        <v>0.4680972631685941</v>
       </c>
       <c r="L24">
-        <v>0.48589663231732189</v>
+        <v>0.4662204098757512</v>
       </c>
       <c r="M24">
-        <v>0.57759922741166614</v>
+        <v>0.485896577269732</v>
       </c>
       <c r="N24">
-        <v>0.68995924555855814</v>
+        <v>0.5775990442193575</v>
       </c>
       <c r="O24">
-        <v>0.77168659873424073</v>
+        <v>0.6899589530855288</v>
       </c>
       <c r="P24">
-        <v>0.88198699821748461</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.7716862237236128</v>
+      </c>
+      <c r="Q24">
+        <v>0.8819864858695124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>7.2073788732338329E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.13832325887405719</v>
+        <v>0.07207380689500395</v>
       </c>
       <c r="D25">
-        <v>0.24462476439274031</v>
+        <v>0.138323156343547</v>
       </c>
       <c r="E25">
-        <v>0.23234720561222119</v>
+        <v>0.2446248066999405</v>
       </c>
       <c r="F25">
-        <v>0.2209559782618333</v>
+        <v>0.2323471477805188</v>
       </c>
       <c r="G25">
-        <v>0.25150924578447692</v>
+        <v>0.2209559049064679</v>
       </c>
       <c r="H25">
-        <v>0.54788789299357332</v>
+        <v>0.2515092619293761</v>
       </c>
       <c r="I25">
-        <v>0.53778368439452184</v>
+        <v>0.5478878317210221</v>
       </c>
       <c r="J25">
-        <v>0.51953921772633416</v>
+        <v>0.5377837209259861</v>
       </c>
       <c r="K25">
-        <v>0.4957782752048695</v>
+        <v>0.519539218657046</v>
       </c>
       <c r="L25">
-        <v>0.49667104285010971</v>
+        <v>0.4957782563972681</v>
       </c>
       <c r="M25">
-        <v>0.53458912640333434</v>
+        <v>0.4966710194630644</v>
       </c>
       <c r="N25">
-        <v>0.62849210680277134</v>
+        <v>0.5345890374959397</v>
       </c>
       <c r="O25">
-        <v>0.72270642175850686</v>
+        <v>0.6284919215440713</v>
       </c>
       <c r="P25">
-        <v>0.81371526715121212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.7227061012401234</v>
+      </c>
+      <c r="Q25">
+        <v>0.813714871593521</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>7.7110244856262403E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.14935455896626029</v>
+        <v>0.07711032013344894</v>
       </c>
       <c r="D26">
-        <v>0.19783169670803399</v>
+        <v>0.1493544894982556</v>
       </c>
       <c r="E26">
-        <v>0.19028000553519031</v>
+        <v>0.1978317064038413</v>
       </c>
       <c r="F26">
-        <v>0.25277349242051822</v>
+        <v>0.1902799928796004</v>
       </c>
       <c r="G26">
-        <v>0.25752723646409759</v>
+        <v>0.2527734679475919</v>
       </c>
       <c r="H26">
-        <v>0.36187136445232593</v>
+        <v>0.2575271884160389</v>
       </c>
       <c r="I26">
-        <v>0.60902000226893227</v>
+        <v>0.3618713394785924</v>
       </c>
       <c r="J26">
-        <v>0.49969797530617271</v>
+        <v>0.6090204305889908</v>
       </c>
       <c r="K26">
-        <v>0.50029232025506265</v>
+        <v>0.4996978822707333</v>
       </c>
       <c r="L26">
-        <v>0.53780358671365058</v>
+        <v>0.5002921032571435</v>
       </c>
       <c r="M26">
-        <v>0.6295750594648285</v>
+        <v>0.5378035702431025</v>
       </c>
       <c r="N26">
-        <v>0.69422154655073931</v>
+        <v>0.6295749110712882</v>
       </c>
       <c r="O26">
-        <v>0.77205472378658191</v>
+        <v>0.6942213062485448</v>
       </c>
       <c r="P26">
-        <v>0.88513081346198774</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.7720543705793258</v>
+      </c>
+      <c r="Q26">
+        <v>0.8851303383983795</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>7.8152574657144494E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>0.14938321533276441</v>
+        <v>0.07815262487406059</v>
       </c>
       <c r="D27">
-        <v>0.19366415639742901</v>
+        <v>0.1493831257237327</v>
       </c>
       <c r="E27">
-        <v>0.1693406164585976</v>
+        <v>0.1936641311855471</v>
       </c>
       <c r="F27">
-        <v>0.22731849602539159</v>
+        <v>0.1693406204308901</v>
       </c>
       <c r="G27">
-        <v>0.22331143460888411</v>
+        <v>0.2273184801775273</v>
       </c>
       <c r="H27">
-        <v>0.25530528889346932</v>
+        <v>0.2233113938040159</v>
       </c>
       <c r="I27">
-        <v>0.43889653776172571</v>
+        <v>0.2553052803192018</v>
       </c>
       <c r="J27">
-        <v>0.35400386621464952</v>
+        <v>0.4388970199602534</v>
       </c>
       <c r="K27">
-        <v>0.33305079755485739</v>
+        <v>0.3540037249362485</v>
       </c>
       <c r="L27">
-        <v>0.32366519255368359</v>
+        <v>0.3330507811204977</v>
       </c>
       <c r="M27">
-        <v>0.37248378517256159</v>
+        <v>0.3236651725617844</v>
       </c>
       <c r="N27">
-        <v>0.37342392105766631</v>
+        <v>0.3724837527967159</v>
       </c>
       <c r="O27">
-        <v>0.41714358107319649</v>
+        <v>0.37342390656359</v>
       </c>
       <c r="P27">
-        <v>0.44276288661404739</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.4171435203830839</v>
+      </c>
+      <c r="Q27">
+        <v>0.4427627503708697</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>6.7611545247580979E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.1288075939348379</v>
+        <v>0.06761155532666126</v>
       </c>
       <c r="D28">
-        <v>0.22114552634240761</v>
+        <v>0.128807560503953</v>
       </c>
       <c r="E28">
-        <v>0.2082285069249005</v>
+        <v>0.2211455574970609</v>
       </c>
       <c r="F28">
-        <v>0.19713971084632151</v>
+        <v>0.2082284575021064</v>
       </c>
       <c r="G28">
-        <v>0.21125472450465579</v>
+        <v>0.1971406716568306</v>
       </c>
       <c r="H28">
-        <v>0.39031461877041218</v>
+        <v>0.2112548005683449</v>
       </c>
       <c r="I28">
-        <v>0.39632912127346293</v>
+        <v>0.3903145767852542</v>
       </c>
       <c r="J28">
-        <v>0.38424084271767728</v>
+        <v>0.3963291195059753</v>
       </c>
       <c r="K28">
-        <v>0.33891572962005911</v>
+        <v>0.384240845513968</v>
       </c>
       <c r="L28">
-        <v>0.33733952121167893</v>
+        <v>0.3389157141076798</v>
       </c>
       <c r="M28">
-        <v>0.33397315253805843</v>
+        <v>0.3373395053599925</v>
       </c>
       <c r="N28">
-        <v>0.37646302474162557</v>
+        <v>0.3339731391002593</v>
       </c>
       <c r="O28">
-        <v>0.41349316393029378</v>
+        <v>0.3764629641047721</v>
       </c>
       <c r="P28">
-        <v>0.45221181752857642</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.4134931228803722</v>
+      </c>
+      <c r="Q28">
+        <v>0.4522117757272997</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>7.1055240366653685E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.1358171191775433</v>
+        <v>0.0710552470978766</v>
       </c>
       <c r="D29">
-        <v>0.2338239982119901</v>
+        <v>0.1358170511325808</v>
       </c>
       <c r="E29">
-        <v>0.22067344656484991</v>
+        <v>0.2338240352316929</v>
       </c>
       <c r="F29">
-        <v>0.2050264915290248</v>
+        <v>0.2206734238748521</v>
       </c>
       <c r="G29">
-        <v>0.21571728729015421</v>
+        <v>0.2050264640635564</v>
       </c>
       <c r="H29">
-        <v>0.38788053899151509</v>
+        <v>0.2157172937034497</v>
       </c>
       <c r="I29">
-        <v>0.39455028513250329</v>
+        <v>0.3878804883026702</v>
       </c>
       <c r="J29">
-        <v>0.38367025586207681</v>
+        <v>0.3945502832296588</v>
       </c>
       <c r="K29">
-        <v>0.33822446652642879</v>
+        <v>0.3836703217420258</v>
       </c>
       <c r="L29">
-        <v>0.33771450128715552</v>
+        <v>0.3382244463624978</v>
       </c>
       <c r="M29">
-        <v>0.32303191329118541</v>
+        <v>0.3377144669580092</v>
       </c>
       <c r="N29">
-        <v>0.36388686519008018</v>
+        <v>0.3230318956347539</v>
       </c>
       <c r="O29">
-        <v>0.39558563839465288</v>
+        <v>0.3638868529334022</v>
       </c>
       <c r="P29">
-        <v>0.41460763718778149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.3955855901783131</v>
+      </c>
+      <c r="Q29">
+        <v>0.4146075909657079</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>7.372599432097951E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.13727794652396841</v>
+        <v>0.07372600230360304</v>
       </c>
       <c r="D30">
-        <v>0.22535131658833399</v>
+        <v>0.1372778990637838</v>
       </c>
       <c r="E30">
-        <v>0.21245012266571009</v>
+        <v>0.2253513429266801</v>
       </c>
       <c r="F30">
-        <v>0.19878943958167511</v>
+        <v>0.2124500645103515</v>
       </c>
       <c r="G30">
-        <v>0.21145401723817989</v>
+        <v>0.1987894059887322</v>
       </c>
       <c r="H30">
-        <v>0.37195493608929342</v>
+        <v>0.2114541078437064</v>
       </c>
       <c r="I30">
-        <v>0.37386607897504331</v>
+        <v>0.3719548672195659</v>
       </c>
       <c r="J30">
-        <v>0.37718059708004809</v>
+        <v>0.373866132456935</v>
       </c>
       <c r="K30">
-        <v>0.32776588869253842</v>
+        <v>0.3771806439945336</v>
       </c>
       <c r="L30">
-        <v>0.32824089651657729</v>
+        <v>0.3277658585249118</v>
       </c>
       <c r="M30">
-        <v>0.31649820415492391</v>
+        <v>0.3282408695399158</v>
       </c>
       <c r="N30">
-        <v>0.3533828929029188</v>
+        <v>0.3164981827315648</v>
       </c>
       <c r="O30">
-        <v>0.37855406571059053</v>
+        <v>0.3533828300122054</v>
       </c>
       <c r="P30">
-        <v>0.39861166745584048</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.3785540363668541</v>
+      </c>
+      <c r="Q30">
+        <v>0.3986116240322324</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>6.5977827705335002E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.1228203900149018</v>
+        <v>0.06597784546793325</v>
       </c>
       <c r="D31">
-        <v>0.2176047639983778</v>
+        <v>0.1228202771735084</v>
       </c>
       <c r="E31">
-        <v>0.20085756805877761</v>
+        <v>0.2176047780332437</v>
       </c>
       <c r="F31">
-        <v>0.1912606202979103</v>
+        <v>0.2008575215964203</v>
       </c>
       <c r="G31">
-        <v>0.20255344714351539</v>
+        <v>0.1912605939143127</v>
       </c>
       <c r="H31">
-        <v>0.35326674654256401</v>
+        <v>0.2025534369266046</v>
       </c>
       <c r="I31">
-        <v>0.37925787972964958</v>
+        <v>0.3532666930519712</v>
       </c>
       <c r="J31">
-        <v>0.38324086871029173</v>
+        <v>0.3792578928567043</v>
       </c>
       <c r="K31">
-        <v>0.32421945884268938</v>
+        <v>0.3832407815920809</v>
       </c>
       <c r="L31">
-        <v>0.335116739318288</v>
+        <v>0.3242194374573498</v>
       </c>
       <c r="M31">
-        <v>0.32776435127254377</v>
+        <v>0.3351166881609974</v>
       </c>
       <c r="N31">
-        <v>0.35603901837862723</v>
+        <v>0.3277643171723721</v>
       </c>
       <c r="O31">
-        <v>0.3888607671158355</v>
+        <v>0.3560389841763139</v>
       </c>
       <c r="P31">
-        <v>0.40196906333796772</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.3888607461169618</v>
+      </c>
+      <c r="Q31">
+        <v>0.4019690393037577</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>6.7322441573736402E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.1319537797264152</v>
+        <v>0.06732245442153219</v>
       </c>
       <c r="D32">
-        <v>0.23042621378697731</v>
+        <v>0.1319537404596419</v>
       </c>
       <c r="E32">
-        <v>0.21741271199375861</v>
+        <v>0.2304262356412616</v>
       </c>
       <c r="F32">
-        <v>0.2005869610662824</v>
+        <v>0.2174125704905181</v>
       </c>
       <c r="G32">
-        <v>0.21165438095170691</v>
+        <v>0.2005868966512312</v>
       </c>
       <c r="H32">
-        <v>0.40194134243033469</v>
+        <v>0.2116543133702972</v>
       </c>
       <c r="I32">
-        <v>0.39830736220235369</v>
+        <v>0.4019412913370213</v>
       </c>
       <c r="J32">
-        <v>0.38680699323095608</v>
+        <v>0.3983073550826738</v>
       </c>
       <c r="K32">
-        <v>0.34851941372045803</v>
+        <v>0.3868069952281936</v>
       </c>
       <c r="L32">
-        <v>0.35078350831485849</v>
+        <v>0.3485193804271893</v>
       </c>
       <c r="M32">
-        <v>0.35688538863613711</v>
+        <v>0.3507834811477066</v>
       </c>
       <c r="N32">
-        <v>0.40940252159817042</v>
+        <v>0.3568853491101286</v>
       </c>
       <c r="O32">
-        <v>0.46296287986689427</v>
+        <v>0.4094024885281228</v>
       </c>
       <c r="P32">
-        <v>0.51528477258812666</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.4629628380515824</v>
+      </c>
+      <c r="Q32">
+        <v>0.5152846878839362</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>7.3283567382376971E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.13953312416834959</v>
+        <v>0.07328357215055301</v>
       </c>
       <c r="D33">
-        <v>0.23568790112540941</v>
+        <v>0.1395330648188582</v>
       </c>
       <c r="E33">
-        <v>0.22409447333079249</v>
+        <v>0.2356877119386196</v>
       </c>
       <c r="F33">
-        <v>0.2060027950325026</v>
+        <v>0.2240944124308745</v>
       </c>
       <c r="G33">
-        <v>0.22375327122677119</v>
+        <v>0.2060027567841431</v>
       </c>
       <c r="H33">
-        <v>0.40881025806066518</v>
+        <v>0.2237532759302964</v>
       </c>
       <c r="I33">
-        <v>0.40634973738225372</v>
+        <v>0.4088101910071041</v>
       </c>
       <c r="J33">
-        <v>0.39607283492944279</v>
+        <v>0.4063497509761359</v>
       </c>
       <c r="K33">
-        <v>0.37003067185686911</v>
+        <v>0.3960728363067997</v>
       </c>
       <c r="L33">
-        <v>0.36513136744048391</v>
+        <v>0.3700306402253642</v>
       </c>
       <c r="M33">
-        <v>0.36658319872182132</v>
+        <v>0.36513133057446</v>
       </c>
       <c r="N33">
-        <v>0.40867403300255822</v>
+        <v>0.3665831422143787</v>
       </c>
       <c r="O33">
-        <v>0.45645633912738592</v>
+        <v>0.4086739800538856</v>
       </c>
       <c r="P33">
-        <v>0.50754188519800902</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.4564562595914496</v>
+      </c>
+      <c r="Q33">
+        <v>0.5075418046920924</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>7.142689497626592E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.1396084386061972</v>
+        <v>0.0714269221266253</v>
       </c>
       <c r="D34">
-        <v>0.23668100575534379</v>
+        <v>0.1396083447200996</v>
       </c>
       <c r="E34">
-        <v>0.21917841449130751</v>
+        <v>0.2366810321124688</v>
       </c>
       <c r="F34">
-        <v>0.20741801440785351</v>
+        <v>0.2191783468380341</v>
       </c>
       <c r="G34">
-        <v>0.22039324906096561</v>
+        <v>0.2074179505705004</v>
       </c>
       <c r="H34">
-        <v>0.40503115850967569</v>
+        <v>0.2203932540784289</v>
       </c>
       <c r="I34">
-        <v>0.39443861961870408</v>
+        <v>0.4050311165440605</v>
       </c>
       <c r="J34">
-        <v>0.3857244701164062</v>
+        <v>0.3944386417676374</v>
       </c>
       <c r="K34">
-        <v>0.37828542869031939</v>
+        <v>0.3857244878820223</v>
       </c>
       <c r="L34">
-        <v>0.3689395695379098</v>
+        <v>0.3782854106911435</v>
       </c>
       <c r="M34">
-        <v>0.3675675546916124</v>
+        <v>0.3689395502945599</v>
       </c>
       <c r="N34">
-        <v>0.39722843034373179</v>
+        <v>0.3675675097317403</v>
       </c>
       <c r="O34">
-        <v>0.43563037281680789</v>
+        <v>0.3972284564755234</v>
       </c>
       <c r="P34">
-        <v>0.48091012407673028</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.435630326592596</v>
+      </c>
+      <c r="Q34">
+        <v>0.4809100786623229</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>7.1376284106944327E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.13029648662115759</v>
+        <v>0.0713763049550569</v>
       </c>
       <c r="D35">
-        <v>0.2248489052276815</v>
+        <v>0.1302964263927209</v>
       </c>
       <c r="E35">
-        <v>0.21263889100487199</v>
+        <v>0.2248489372549899</v>
       </c>
       <c r="F35">
-        <v>0.19941806983336891</v>
+        <v>0.2126387807895004</v>
       </c>
       <c r="G35">
-        <v>0.21423372171048019</v>
+        <v>0.1994178907384353</v>
       </c>
       <c r="H35">
-        <v>0.39709021512743592</v>
+        <v>0.2142337258156328</v>
       </c>
       <c r="I35">
-        <v>0.40060993276220619</v>
+        <v>0.3970901537782378</v>
       </c>
       <c r="J35">
-        <v>0.38927361068190319</v>
+        <v>0.4006099772203436</v>
       </c>
       <c r="K35">
-        <v>0.35464255172077591</v>
+        <v>0.3892736214500683</v>
       </c>
       <c r="L35">
-        <v>0.35940816507287632</v>
+        <v>0.3546425387951672</v>
       </c>
       <c r="M35">
-        <v>0.35134527042240249</v>
+        <v>0.3594081449076176</v>
       </c>
       <c r="N35">
-        <v>0.38724038260395421</v>
+        <v>0.3513452453941771</v>
       </c>
       <c r="O35">
-        <v>0.42728657249394553</v>
+        <v>0.3872403579862161</v>
       </c>
       <c r="P35">
-        <v>0.45839793619477298</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.4272865295775859</v>
+      </c>
+      <c r="Q35">
+        <v>0.458397881305098</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>7.1910438596963139E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.13734913225016071</v>
+        <v>0.071910447912076</v>
       </c>
       <c r="D36">
-        <v>0.22553599276935021</v>
+        <v>0.1373490944696011</v>
       </c>
       <c r="E36">
-        <v>0.2134304523698754</v>
+        <v>0.225536002630079</v>
       </c>
       <c r="F36">
-        <v>0.2009681997886891</v>
+        <v>0.2134303446588782</v>
       </c>
       <c r="G36">
-        <v>0.21388083837235619</v>
+        <v>0.2009680071947385</v>
       </c>
       <c r="H36">
-        <v>0.35862152318518548</v>
+        <v>0.2138806885070371</v>
       </c>
       <c r="I36">
-        <v>0.36994963542102521</v>
+        <v>0.3586214905088299</v>
       </c>
       <c r="J36">
-        <v>0.3729540977525449</v>
+        <v>0.3699496511087604</v>
       </c>
       <c r="K36">
-        <v>0.32600389681240188</v>
+        <v>0.372954101931353</v>
       </c>
       <c r="L36">
-        <v>0.32601773696020647</v>
+        <v>0.326003875171899</v>
       </c>
       <c r="M36">
-        <v>0.32979623644844441</v>
+        <v>0.3260177181572281</v>
       </c>
       <c r="N36">
-        <v>0.34845753554255832</v>
+        <v>0.3297962065534957</v>
       </c>
       <c r="O36">
-        <v>0.38229155231999518</v>
+        <v>0.348457508933338</v>
       </c>
       <c r="P36">
-        <v>0.39262322819675038</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.3822915200352148</v>
+      </c>
+      <c r="Q36">
+        <v>0.3926231979498295</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.1538675132009921</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.34610654290578818</v>
+        <v>0.1538673298209442</v>
       </c>
       <c r="D37">
-        <v>0.29863784462761112</v>
+        <v>0.346106524553021</v>
       </c>
       <c r="E37">
-        <v>0.32652233283138787</v>
+        <v>0.2986378486060356</v>
       </c>
       <c r="F37">
-        <v>0.53769882142521597</v>
+        <v>0.3265223766581042</v>
       </c>
       <c r="G37">
-        <v>0.56320075060278696</v>
+        <v>0.5376988972773785</v>
       </c>
       <c r="H37">
-        <v>0.57968717858466745</v>
+        <v>0.5632008281628703</v>
       </c>
       <c r="I37">
-        <v>0.57458932510841365</v>
+        <v>0.579687133047436</v>
       </c>
       <c r="J37">
-        <v>0.61430503098487144</v>
+        <v>0.5745892199961697</v>
       </c>
       <c r="K37">
-        <v>0.66821182300909066</v>
+        <v>0.6143048969732327</v>
       </c>
       <c r="L37">
-        <v>0.71641150358113981</v>
+        <v>0.6682116280801849</v>
       </c>
       <c r="M37">
-        <v>0.7865731693190432</v>
+        <v>0.7164113396800766</v>
       </c>
       <c r="N37">
-        <v>0.79397023091359042</v>
+        <v>0.7865729083236106</v>
       </c>
       <c r="O37">
-        <v>0.81149070036210935</v>
+        <v>0.7939698007161867</v>
       </c>
       <c r="P37">
-        <v>0.82105931158794532</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.8114900153449842</v>
+      </c>
+      <c r="Q37">
+        <v>0.8210584832181896</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.1012087863483502</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.25049618368661308</v>
+        <v>0.1012087112576064</v>
       </c>
       <c r="D38">
-        <v>0.25035323811055382</v>
+        <v>0.2504961619465924</v>
       </c>
       <c r="E38">
-        <v>0.27682310854199721</v>
+        <v>0.2503534079951028</v>
       </c>
       <c r="F38">
-        <v>0.45568766486769691</v>
+        <v>0.2768229966569984</v>
       </c>
       <c r="G38">
-        <v>0.35831297346051549</v>
+        <v>0.4556876885269884</v>
       </c>
       <c r="H38">
-        <v>0.27369562562943789</v>
+        <v>0.3583130209671</v>
       </c>
       <c r="I38">
-        <v>0.32539293637620492</v>
+        <v>0.2736956486662631</v>
       </c>
       <c r="J38">
-        <v>0.39406450480492988</v>
+        <v>0.3253929092158157</v>
       </c>
       <c r="K38">
-        <v>0.46248329114775483</v>
+        <v>0.394064486863319</v>
       </c>
       <c r="L38">
-        <v>0.51363873670453608</v>
+        <v>0.4624831987871203</v>
       </c>
       <c r="M38">
-        <v>0.55395568238789439</v>
+        <v>0.5136386196016791</v>
       </c>
       <c r="N38">
-        <v>0.59576339051631799</v>
+        <v>0.5539555042363621</v>
       </c>
       <c r="O38">
-        <v>0.62084816648265928</v>
+        <v>0.5957632004866138</v>
       </c>
       <c r="P38">
-        <v>0.63562397097688672</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.6208480542507225</v>
+      </c>
+      <c r="Q38">
+        <v>0.6356237972843082</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>9.7584640937117925E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.23146208933209031</v>
+        <v>0.09758456319262511</v>
       </c>
       <c r="D39">
-        <v>0.22144832048771279</v>
+        <v>0.2314620481932795</v>
       </c>
       <c r="E39">
-        <v>0.21441557995783089</v>
+        <v>0.2214482926222244</v>
       </c>
       <c r="F39">
-        <v>0.3452002119177916</v>
+        <v>0.2144154579016471</v>
       </c>
       <c r="G39">
-        <v>0.27678148285784282</v>
+        <v>0.34520022074552</v>
       </c>
       <c r="H39">
-        <v>0.25986204316450939</v>
+        <v>0.2767815120325013</v>
       </c>
       <c r="I39">
-        <v>0.30794420469514711</v>
+        <v>0.2598620595565019</v>
       </c>
       <c r="J39">
-        <v>0.35861550923766028</v>
+        <v>0.3079441966457475</v>
       </c>
       <c r="K39">
-        <v>0.38579145745701438</v>
+        <v>0.3586155010565271</v>
       </c>
       <c r="L39">
-        <v>0.44380395114881471</v>
+        <v>0.3857914044495613</v>
       </c>
       <c r="M39">
-        <v>0.44947883485489382</v>
+        <v>0.4438038657452054</v>
       </c>
       <c r="N39">
-        <v>0.51218382246291783</v>
+        <v>0.4494785604850282</v>
       </c>
       <c r="O39">
-        <v>0.56009339351419618</v>
+        <v>0.5121827053032617</v>
       </c>
       <c r="P39">
-        <v>0.59021099502147023</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.5600932347028207</v>
+      </c>
+      <c r="Q39">
+        <v>0.5902107626358033</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.13246536416156801</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.13019837980365079</v>
+        <v>0.1324653118882822</v>
       </c>
       <c r="D40">
-        <v>0.2028283095123356</v>
+        <v>0.1301983317981562</v>
       </c>
       <c r="E40">
-        <v>0.26710191077702172</v>
+        <v>0.2028283149631581</v>
       </c>
       <c r="F40">
-        <v>0.36684540396208609</v>
+        <v>0.2671018724295245</v>
       </c>
       <c r="G40">
-        <v>0.37625023089549398</v>
+        <v>0.3668454626931258</v>
       </c>
       <c r="H40">
-        <v>0.44687622722844689</v>
+        <v>0.376250236974558</v>
       </c>
       <c r="I40">
-        <v>0.54469368629378034</v>
+        <v>0.4468761977751574</v>
       </c>
       <c r="J40">
-        <v>0.60177163193911831</v>
+        <v>0.5446935540017955</v>
       </c>
       <c r="K40">
-        <v>0.61626663354405409</v>
+        <v>0.6017714611680048</v>
       </c>
       <c r="L40">
-        <v>0.64484755620050738</v>
+        <v>0.6162664565391337</v>
       </c>
       <c r="M40">
-        <v>0.64798783407778793</v>
+        <v>0.6448473788747321</v>
       </c>
       <c r="N40">
-        <v>0.68546577976478507</v>
+        <v>0.6479876125675023</v>
       </c>
       <c r="O40">
-        <v>0.73200898549382742</v>
+        <v>0.6854653782729425</v>
       </c>
       <c r="P40">
-        <v>0.81550728517144966</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.7320084781589429</v>
+      </c>
+      <c r="Q40">
+        <v>0.8155065242752836</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.17010033724064261</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.48603031161388771</v>
+        <v>0.1701003955162115</v>
       </c>
       <c r="D41">
-        <v>0.48303284490143428</v>
+        <v>0.4860302884524204</v>
       </c>
       <c r="E41">
-        <v>0.57085893731848936</v>
+        <v>0.4830328350730603</v>
       </c>
       <c r="F41">
-        <v>0.59993319938251322</v>
+        <v>0.570858962774207</v>
       </c>
       <c r="G41">
-        <v>0.6330275610771432</v>
+        <v>0.5999332227188172</v>
       </c>
       <c r="H41">
-        <v>0.6691396824905318</v>
+        <v>0.6330276191363594</v>
       </c>
       <c r="I41">
-        <v>0.67058734917407059</v>
+        <v>0.6691396715779774</v>
       </c>
       <c r="J41">
-        <v>0.74235552667456706</v>
+        <v>0.6705873411197297</v>
       </c>
       <c r="K41">
-        <v>0.80390938556342717</v>
+        <v>0.7423554894478127</v>
       </c>
       <c r="L41">
-        <v>0.84047740288633555</v>
+        <v>0.8039093402903194</v>
       </c>
       <c r="M41">
-        <v>0.90175627515432655</v>
+        <v>0.8404773024913074</v>
       </c>
       <c r="N41">
-        <v>0.97934770721495801</v>
+        <v>0.9017561037498442</v>
       </c>
       <c r="O41">
-        <v>1.0079033814068119</v>
+        <v>0.9793474953907906</v>
       </c>
       <c r="P41">
-        <v>1.042065550301019</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>1.007903136903932</v>
+      </c>
+      <c r="Q41">
+        <v>1.042065264722279</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>6.2492141205943222E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.62593980900715429</v>
+        <v>0.06249214485974337</v>
       </c>
       <c r="D42">
-        <v>0.56611661177848427</v>
+        <v>0.6259400201981156</v>
       </c>
       <c r="E42">
-        <v>0.43444416179879919</v>
+        <v>0.5661169088063764</v>
       </c>
       <c r="F42">
-        <v>0.42125581024770159</v>
+        <v>0.4344442978339031</v>
       </c>
       <c r="G42">
-        <v>0.44633928970059378</v>
+        <v>0.4212558737038972</v>
       </c>
       <c r="H42">
-        <v>0.42065227833535068</v>
+        <v>0.4463392393713999</v>
       </c>
       <c r="I42">
-        <v>0.44589414019002149</v>
+        <v>0.4206523028039585</v>
       </c>
       <c r="J42">
-        <v>0.49895116614667362</v>
+        <v>0.4458941167122132</v>
       </c>
       <c r="K42">
-        <v>0.51765988369399785</v>
+        <v>0.4989511448771426</v>
       </c>
       <c r="L42">
-        <v>0.54821377433876795</v>
+        <v>0.5176598748956194</v>
       </c>
       <c r="M42">
-        <v>0.60879335596831852</v>
+        <v>0.548213809169713</v>
       </c>
       <c r="N42">
-        <v>0.63945575105746699</v>
+        <v>0.6087932470652763</v>
       </c>
       <c r="O42">
-        <v>0.64756008355326899</v>
+        <v>0.6394556054475515</v>
       </c>
       <c r="P42">
-        <v>0.68894601233440111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.647559888791749</v>
+      </c>
+      <c r="Q42">
+        <v>0.6889457833283296</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.1009283957905875</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.23873296930550161</v>
+        <v>0.100928457015024</v>
       </c>
       <c r="D43">
-        <v>0.36832181484635518</v>
+        <v>0.238732978537353</v>
       </c>
       <c r="E43">
-        <v>0.44415814434006068</v>
+        <v>0.3683218564743652</v>
       </c>
       <c r="F43">
-        <v>0.35456089466893581</v>
+        <v>0.4441581464149333</v>
       </c>
       <c r="G43">
-        <v>0.35586436893098627</v>
+        <v>0.3545609314740465</v>
       </c>
       <c r="H43">
-        <v>0.39495976908638569</v>
+        <v>0.3558643900862902</v>
       </c>
       <c r="I43">
-        <v>0.44085558054261592</v>
+        <v>0.3949597893036128</v>
       </c>
       <c r="J43">
-        <v>0.53793169353912118</v>
+        <v>0.4408556181822492</v>
       </c>
       <c r="K43">
-        <v>0.53690171686707544</v>
+        <v>0.5379316609522264</v>
       </c>
       <c r="L43">
-        <v>0.56228541521681774</v>
+        <v>0.5369017048377321</v>
       </c>
       <c r="M43">
-        <v>0.58879631361247431</v>
+        <v>0.5622853720421213</v>
       </c>
       <c r="N43">
-        <v>0.62476254539728093</v>
+        <v>0.5887962468751052</v>
       </c>
       <c r="O43">
-        <v>0.65868716759245438</v>
+        <v>0.6247624471062051</v>
       </c>
       <c r="P43">
-        <v>0.69030822974361128</v>
+        <v>0.6586870401591237</v>
+      </c>
+      <c r="Q43">
+        <v>0.6903081735753238</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P43">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>